--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484223_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484223_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8834</v>
+        <v>8.5899</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3729</v>
+        <v>6.4334</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5105</v>
+        <v>2.1565</v>
       </c>
       <c r="G2" t="n">
         <v>7.6608</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1092</v>
+        <v>0.8157</v>
       </c>
       <c r="T2" t="n">
-        <v>0.278</v>
+        <v>0.3385</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8312</v>
+        <v>0.4772</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2772</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0023</v>
+        <v>4.8195</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7853</v>
+        <v>2.6842</v>
       </c>
       <c r="F3" t="n">
-        <v>2.217</v>
+        <v>2.1353</v>
       </c>
       <c r="G3" t="n">
         <v>3.5431</v>
@@ -688,13 +688,13 @@
         <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4945</v>
+        <v>1.3117</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5806</v>
+        <v>0.4795</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9139</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.9414</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3608</v>
+        <v>3.7135</v>
       </c>
       <c r="E4" t="n">
-        <v>2.161</v>
+        <v>1.5137</v>
       </c>
       <c r="F4" t="n">
         <v>2.1998</v>
@@ -766,10 +766,10 @@
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2326</v>
+        <v>0.5853</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8035</v>
+        <v>0.1562</v>
       </c>
       <c r="U4" t="n">
         <v>0.4291</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.756</v>
+        <v>2.0927</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6237</v>
+        <v>1.9876</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1323</v>
+        <v>0.1051</v>
       </c>
       <c r="G5" t="n">
         <v>3.7455</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4034</v>
+        <v>-0.0668</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5447</v>
+        <v>-0.1808</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1413</v>
+        <v>0.1141</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6093</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0567</v>
+        <v>1.4301</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0756</v>
+        <v>-0.0906</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9811</v>
+        <v>1.5206</v>
       </c>
       <c r="G6" t="n">
-        <v>1.635</v>
+        <v>1.201</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7994</v>
+        <v>0.2034</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8356</v>
+        <v>0.9976</v>
       </c>
       <c r="J6" t="n">
-        <v>0.841</v>
+        <v>0.8716</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6792</v>
+        <v>0.1433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1619</v>
+        <v>0.7284</v>
       </c>
       <c r="M6" t="n">
-        <v>0.794</v>
+        <v>0.3294</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1203</v>
+        <v>0.0601</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6737</v>
+        <v>0.2692</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5585</v>
+        <v>0.229</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1294</v>
+        <v>0.0145</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4291</v>
+        <v>0.2145</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0521</v>
+        <v>1.2059</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5785</v>
+        <v>1.8413</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5264</v>
+        <v>-0.6354</v>
       </c>
       <c r="G7" t="n">
         <v>0.3457</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.821</v>
+        <v>-0.6672</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4099</v>
+        <v>-0.1471</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4111</v>
+        <v>-0.5201</v>
       </c>
       <c r="V7" t="n">
         <v>0.9414</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0178</v>
+        <v>0.915</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3939</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4117</v>
+        <v>0.9811</v>
       </c>
       <c r="G8" t="n">
-        <v>1.201</v>
+        <v>1.635</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2034</v>
+        <v>0.7994</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9976</v>
+        <v>0.8356</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8716</v>
+        <v>0.841</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1433</v>
+        <v>0.6792</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7284</v>
+        <v>0.1619</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3294</v>
+        <v>0.794</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0601</v>
+        <v>0.1203</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2692</v>
+        <v>0.6737</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1832</v>
+        <v>0.4168</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2888</v>
+        <v>-0.0123</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1056</v>
+        <v>0.4291</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9461000000000001</v>
+        <v>-0.0396</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3762</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4301</v>
+        <v>-0.5663</v>
       </c>
       <c r="G9" t="n">
         <v>-0.284</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8626</v>
+        <v>0.877</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5657</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.297</v>
+        <v>0.1608</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3867</v>
+        <v>-0.2874</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001</v>
+        <v>0.2638</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3877</v>
+        <v>-0.5512</v>
       </c>
       <c r="G10" t="n">
         <v>0.2613</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0154</v>
+        <v>0.0839</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4099</v>
+        <v>-0.1471</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3944</v>
+        <v>0.231</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2734</v>
+        <v>-0.5245</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3639</v>
+        <v>-1.6967</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0904</v>
+        <v>1.1722</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3628</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2427</v>
+        <v>0.5062</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3218</v>
+        <v>0.3454</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0791</v>
+        <v>0.1608</v>
       </c>
       <c r="V11" t="n">
         <v>0.3321</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2113</v>
+        <v>-2.3512</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8174</v>
+        <v>-2.1207</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3939</v>
+        <v>-0.2305</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7012</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4667</v>
+        <v>0.3267</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6274</v>
+        <v>0.324</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1607</v>
+        <v>0.0027</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6093</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8169</v>
+        <v>-3.5717</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9607</v>
+        <v>-4.2329</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1438</v>
+        <v>0.6612</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4407</v>
@@ -1468,13 +1468,13 @@
         <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0554</v>
+        <v>0.1898</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5777</v>
+        <v>0.1501</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4777</v>
+        <v>0.0398</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.3869</v>
+        <v>15.9922</v>
       </c>
       <c r="E14" t="n">
-        <v>6.438299999999997</v>
+        <v>7.0437</v>
       </c>
       <c r="F14" t="n">
-        <v>8.948499999999999</v>
+        <v>8.948399999999999</v>
       </c>
       <c r="G14" t="n">
         <v>17.9505</v>
@@ -1546,10 +1546,10 @@
         <v>10.7438</v>
       </c>
       <c r="S14" t="n">
-        <v>4.003000000000001</v>
+        <v>4.608099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4318</v>
+        <v>2.0371</v>
       </c>
       <c r="U14" t="n">
         <v>2.5712</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0291</v>
+        <v>3.4659</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0685</v>
+        <v>3.3719</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0394</v>
+        <v>0.094</v>
       </c>
       <c r="G15" t="n">
         <v>1.4095</v>
@@ -1624,13 +1624,13 @@
         <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6576</v>
+        <v>-0.2208</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0081</v>
+        <v>0.1416</v>
       </c>
       <c r="V15" t="n">
         <v>1.4959</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0759</v>
+        <v>0.8821</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2013</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2772</v>
+        <v>0.0742</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4686</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0295</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.806</v>
+        <v>-0.1993</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2235</v>
+        <v>0.1278</v>
       </c>
       <c r="V16" t="n">
         <v>0.6642</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0974</v>
+        <v>0.4705</v>
       </c>
       <c r="E17" t="n">
         <v>0.9897</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.087</v>
+        <v>-0.5192</v>
       </c>
       <c r="G17" t="n">
         <v>1.8639</v>
@@ -1780,13 +1780,13 @@
         <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7659</v>
+        <v>-0.1981</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0246</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7413</v>
+        <v>-0.1734</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6093</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1147</v>
+        <v>-0.4595</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0559</v>
+        <v>-0.5615</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0587</v>
+        <v>0.102</v>
       </c>
       <c r="G18" t="n">
         <v>-3.0463</v>
@@ -1858,13 +1858,13 @@
         <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3456</v>
+        <v>0.0007</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2588</v>
+        <v>-0.2468</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0868</v>
+        <v>0.2475</v>
       </c>
       <c r="V18" t="n">
         <v>1.2186</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3011</v>
+        <v>-1.4151</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3048</v>
+        <v>0.0014</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6058</v>
+        <v>-1.4165</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2301</v>
@@ -1936,13 +1936,13 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2663</v>
+        <v>-0.3804</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0083</v>
+        <v>-0.295</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2746</v>
+        <v>-0.0854</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6093</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1501</v>
+        <v>-1.4202</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-0.4489</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2968</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4004</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3943</v>
+        <v>-0.6644</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.5034</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4865</v>
+        <v>-0.161</v>
       </c>
       <c r="V20" t="n">
         <v>0.2772</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5785</v>
+        <v>-2.525</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6066</v>
+        <v>-2.3073</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9719</v>
+        <v>-0.2177</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0943</v>
+        <v>-3.2122</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9453</v>
+        <v>-2.4569</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.149</v>
+        <v>-0.7552</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2419</v>
+        <v>-1.2901</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3633</v>
+        <v>-0.6703</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1214</v>
+        <v>-0.6198</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8524</v>
+        <v>-1.9221</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.582</v>
+        <v>-1.7866</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2704</v>
+        <v>-0.1354</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8832</v>
+        <v>-0.0041</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5422</v>
+        <v>0.0497</v>
       </c>
       <c r="U21" t="n">
-        <v>0.341</v>
+        <v>-0.0537</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6326</v>
+        <v>-3.4238</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3073</v>
+        <v>-2.3144</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3253</v>
+        <v>-1.1095</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2122</v>
+        <v>-2.0943</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4569</v>
+        <v>-1.9453</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7552</v>
+        <v>-0.149</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2901</v>
+        <v>-0.2419</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6703</v>
+        <v>-0.3633</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6198</v>
+        <v>0.1214</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9221</v>
+        <v>-1.8524</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7866</v>
+        <v>-1.582</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1354</v>
+        <v>-0.2704</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R22" t="n">
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1117</v>
+        <v>0.0379</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0497</v>
+        <v>-0.1656</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1613</v>
+        <v>0.2035</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8865</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9553</v>
+        <v>-3.9124</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6036</v>
+        <v>-2.8058</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3517</v>
+        <v>-1.1066</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6683</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4005</v>
+        <v>-0.3576</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.22</v>
+        <v>-0.4222</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1805</v>
+        <v>0.0646</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2772</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5105</v>
+        <v>-5.027</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0859</v>
+        <v>-5.6815</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5754</v>
+        <v>0.6544</v>
       </c>
       <c r="G24" t="n">
         <v>-5.1037</v>
@@ -2326,13 +2326,13 @@
         <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6059</v>
+        <v>-0.1224</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.806</v>
+        <v>-0.4015</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2001</v>
+        <v>0.2791</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3869</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.387</v>
+        <v>-13.3645</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.9483</v>
+        <v>-8.948399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.4384</v>
+        <v>-4.416200000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-17.9505</v>
@@ -2404,13 +2404,13 @@
         <v>14.6507</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.0029</v>
+        <v>-1.9807</v>
       </c>
       <c r="T25" t="n">
         <v>-2.5711</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4317</v>
+        <v>0.5906</v>
       </c>
       <c r="V25" t="n">
         <v>2.6597</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484223_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484223_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4301</v>
+        <v>1.2059</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0906</v>
+        <v>1.8413</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5206</v>
+        <v>-0.6354</v>
       </c>
       <c r="G6" t="n">
-        <v>1.201</v>
+        <v>0.3457</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2034</v>
+        <v>-0.4768</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9976</v>
+        <v>0.8225</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8716</v>
+        <v>0.7698</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1433</v>
+        <v>0.0819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7284</v>
+        <v>0.6879</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3294</v>
+        <v>-0.4241</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0601</v>
+        <v>-0.5587</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2692</v>
+        <v>0.1346</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>0.229</v>
+        <v>-0.6672</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0145</v>
+        <v>-0.1471</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2145</v>
+        <v>-0.5201</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2059</v>
+        <v>0.915</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8413</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6354</v>
+        <v>0.9811</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3457</v>
+        <v>1.635</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4768</v>
+        <v>0.7994</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8225</v>
+        <v>0.8356</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7698</v>
+        <v>0.841</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0819</v>
+        <v>0.6792</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6879</v>
+        <v>0.1619</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4241</v>
+        <v>0.794</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5587</v>
+        <v>0.1203</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1346</v>
+        <v>0.6737</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6672</v>
+        <v>0.4168</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1471</v>
+        <v>-0.0123</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5201</v>
+        <v>0.4291</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9414</v>
+        <v>-0.9414</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.915</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.6976</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9811</v>
+        <v>1.5206</v>
       </c>
       <c r="G8" t="n">
-        <v>1.635</v>
+        <v>0.594</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7994</v>
+        <v>0.2034</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8356</v>
+        <v>0.3906</v>
       </c>
       <c r="J8" t="n">
-        <v>0.841</v>
+        <v>0.2647</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6792</v>
+        <v>0.1433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1619</v>
+        <v>0.1214</v>
       </c>
       <c r="M8" t="n">
-        <v>0.794</v>
+        <v>0.3294</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1203</v>
+        <v>0.0601</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6737</v>
+        <v>0.2692</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4168</v>
+        <v>0.229</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0123</v>
+        <v>0.0145</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4291</v>
+        <v>0.2145</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0396</v>
+        <v>0.607</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5663</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.284</v>
+        <v>0.607</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1888</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0951</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0059</v>
+        <v>0.607</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0346</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2898</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1542</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1356</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.877</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7161999999999999</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1608</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1234,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2874</v>
+        <v>-0.0396</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2638</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5512</v>
+        <v>-0.5663</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2613</v>
+        <v>-0.284</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.089</v>
+        <v>-0.1888</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3504</v>
+        <v>-0.0951</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4109</v>
+        <v>0.0059</v>
       </c>
       <c r="K10" t="n">
-        <v>0.33</v>
+        <v>-0.0346</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1496</v>
+        <v>-0.2898</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.419</v>
+        <v>-0.1542</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2694</v>
+        <v>-0.1356</v>
       </c>
       <c r="P10" t="n">
         <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0839</v>
+        <v>0.877</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1471</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.231</v>
+        <v>0.1608</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1250,12 +1295,17 @@
       </c>
       <c r="X10" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5245</v>
+        <v>-0.2874</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6967</v>
+        <v>0.2638</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1722</v>
+        <v>-0.5512</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3628</v>
+        <v>0.2613</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1901</v>
+        <v>-0.089</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1727</v>
+        <v>0.3504</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3426</v>
+        <v>0.4109</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0359</v>
+        <v>0.33</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3067</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0202</v>
+        <v>-0.1496</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1542</v>
+        <v>-0.419</v>
       </c>
       <c r="O11" t="n">
-        <v>0.134</v>
+        <v>0.2694</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5062</v>
+        <v>0.0839</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3454</v>
+        <v>-0.1471</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1608</v>
+        <v>0.231</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3512</v>
+        <v>-0.5245</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1207</v>
+        <v>-1.6967</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2305</v>
+        <v>1.1722</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7012</v>
+        <v>-1.3628</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0133</v>
+        <v>-0.1901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6879</v>
+        <v>-1.1727</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4913</v>
+        <v>-1.3426</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0614</v>
+        <v>-0.0359</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5527</v>
+        <v>-1.3067</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2099</v>
+        <v>-0.0202</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0747</v>
+        <v>-0.1542</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1352</v>
+        <v>0.134</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3267</v>
+        <v>0.5062</v>
       </c>
       <c r="T12" t="n">
-        <v>0.324</v>
+        <v>0.3454</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0027</v>
+        <v>0.1608</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6093</v>
+        <v>0.3321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6093</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5717</v>
+        <v>-2.3512</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2329</v>
+        <v>-2.1207</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6612</v>
+        <v>-0.2305</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4407</v>
+        <v>-0.7012</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7644</v>
+        <v>-0.0133</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3237</v>
+        <v>-0.6879</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2808</v>
+        <v>-0.4913</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2008</v>
+        <v>0.0614</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0799</v>
+        <v>-0.5527</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1599</v>
+        <v>-0.2099</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5636</v>
+        <v>-0.0747</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4037</v>
+        <v>-0.1352</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.3208</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.1022</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1898</v>
+        <v>0.3267</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1501</v>
+        <v>0.324</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0398</v>
+        <v>0.0027</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.9922</v>
+        <v>-3.5717</v>
       </c>
       <c r="E14" t="n">
-        <v>7.0437</v>
+        <v>-4.2329</v>
       </c>
       <c r="F14" t="n">
-        <v>8.948399999999999</v>
+        <v>0.6612</v>
       </c>
       <c r="G14" t="n">
-        <v>17.9505</v>
+        <v>-0.4407</v>
       </c>
       <c r="H14" t="n">
-        <v>9.1854</v>
+        <v>-0.7644</v>
       </c>
       <c r="I14" t="n">
-        <v>8.765299999999998</v>
+        <v>0.3237</v>
       </c>
       <c r="J14" t="n">
-        <v>15.7792</v>
+        <v>-0.2808</v>
       </c>
       <c r="K14" t="n">
-        <v>10.3786</v>
+        <v>-0.2008</v>
       </c>
       <c r="L14" t="n">
-        <v>5.4007</v>
+        <v>-0.0799</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1715</v>
+        <v>-0.1599</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1931</v>
+        <v>-0.5636</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3644</v>
+        <v>0.4037</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.9068</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.6506</v>
+        <v>-4.1022</v>
       </c>
       <c r="R14" t="n">
-        <v>10.7438</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>4.608099999999999</v>
+        <v>0.1898</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0371</v>
+        <v>0.1501</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5712</v>
+        <v>0.0398</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.6595</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8781</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.5377</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4659</v>
+        <v>15.9922</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3719</v>
+        <v>7.0437</v>
       </c>
       <c r="F15" t="n">
-        <v>0.094</v>
+        <v>8.948400000000003</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4095</v>
+        <v>17.9505</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1533</v>
+        <v>9.1854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2562</v>
+        <v>8.765300000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2384</v>
+        <v>15.7793</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5771</v>
+        <v>10.3786</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6613</v>
+        <v>5.400699999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8289</v>
+        <v>2.1715</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4239</v>
+        <v>-1.1931</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4051</v>
+        <v>3.3644</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>-3.9068</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-14.6506</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>10.7438</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2208</v>
+        <v>4.608099999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3624</v>
+        <v>2.0371</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1416</v>
+        <v>2.5712</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4959</v>
+        <v>-2.6595</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4959</v>
+        <v>3.8781</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-6.5377</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8821</v>
+        <v>3.4659</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8080000000000001</v>
+        <v>3.3719</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0742</v>
+        <v>0.094</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4686</v>
+        <v>1.4095</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5229</v>
+        <v>1.1533</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0543</v>
+        <v>0.2562</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.016</v>
+        <v>2.2384</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0639</v>
+        <v>1.5771</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0799</v>
+        <v>0.6613</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4526</v>
+        <v>-0.8289</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5868</v>
+        <v>-0.4239</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1342</v>
+        <v>-0.4051</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.2208</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1993</v>
+        <v>-0.3624</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1278</v>
+        <v>0.1416</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>1.4959</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4705</v>
+        <v>0.8821</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9897</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5192</v>
+        <v>0.0742</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8639</v>
+        <v>-1.4686</v>
       </c>
       <c r="H17" t="n">
-        <v>2.174</v>
+        <v>-1.5229</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3101</v>
+        <v>0.0543</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9677</v>
+        <v>-0.016</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3331</v>
+        <v>0.0639</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6346000000000001</v>
+        <v>-0.0799</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1038</v>
+        <v>-1.4526</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1591</v>
+        <v>-1.5868</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9447</v>
+        <v>0.1342</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1981</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0246</v>
+        <v>-0.1993</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1734</v>
+        <v>0.1278</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>0.6642</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4595</v>
+        <v>0.4705</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5615</v>
+        <v>0.9897</v>
       </c>
       <c r="F18" t="n">
-        <v>0.102</v>
+        <v>-0.5192</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0463</v>
+        <v>1.8639</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6841</v>
+        <v>2.174</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3622</v>
+        <v>-0.3101</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.338</v>
+        <v>2.9677</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3252</v>
+        <v>2.3331</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0128</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7083</v>
+        <v>-1.1038</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3589</v>
+        <v>-0.1591</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3494</v>
+        <v>-0.9447</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.3674</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.5627</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.0007</v>
+        <v>-0.1981</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2468</v>
+        <v>-0.0246</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2475</v>
+        <v>-0.1734</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2186</v>
+        <v>-0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4151</v>
+        <v>-0.4595</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0014</v>
+        <v>-0.5615</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4165</v>
+        <v>0.102</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2301</v>
+        <v>-3.0463</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1878</v>
+        <v>-1.6841</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4179</v>
+        <v>-1.3622</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6637999999999999</v>
+        <v>-1.338</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6766</v>
+        <v>-1.3252</v>
       </c>
       <c r="L19" t="n">
         <v>-0.0128</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8939</v>
+        <v>-1.7083</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4889</v>
+        <v>-0.3589</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4051</v>
+        <v>-1.3494</v>
       </c>
       <c r="P19" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9767</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3804</v>
+        <v>0.0007</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.295</v>
+        <v>-0.2468</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0854</v>
+        <v>0.2475</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4202</v>
+        <v>-1.4151</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4489</v>
+        <v>0.0014</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-1.4165</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4004</v>
+        <v>-0.2301</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1195</v>
+        <v>0.1878</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.5199</v>
+        <v>-0.4179</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2227</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6782</v>
+        <v>0.6766</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9009</v>
+        <v>-0.0128</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1777</v>
+        <v>-0.8939</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5587</v>
+        <v>-0.4889</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.619</v>
+        <v>-0.4051</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6644</v>
+        <v>-0.3804</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5034</v>
+        <v>-0.295</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.161</v>
+        <v>-0.0854</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.525</v>
+        <v>-1.4202</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3073</v>
+        <v>-0.4489</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2177</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2122</v>
+        <v>-2.4004</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4569</v>
+        <v>1.1195</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7552</v>
+        <v>-3.5199</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2901</v>
+        <v>-0.2227</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6703</v>
+        <v>1.6782</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6198</v>
+        <v>-1.9009</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9221</v>
+        <v>-2.1777</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7866</v>
+        <v>-0.5587</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1354</v>
+        <v>-1.619</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0041</v>
+        <v>-0.6644</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0497</v>
+        <v>-0.5034</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0537</v>
+        <v>-0.161</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4238</v>
+        <v>-2.525</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3144</v>
+        <v>-2.3073</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1095</v>
+        <v>-0.2177</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0943</v>
+        <v>-3.2122</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9453</v>
+        <v>-2.4569</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.149</v>
+        <v>-0.7552</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2419</v>
+        <v>-1.2901</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3633</v>
+        <v>-0.6703</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1214</v>
+        <v>-0.6198</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8524</v>
+        <v>-1.9221</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.582</v>
+        <v>-1.7866</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2704</v>
+        <v>-0.1354</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0379</v>
+        <v>-0.0041</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1656</v>
+        <v>0.0497</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2035</v>
+        <v>-0.0537</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9124</v>
+        <v>-3.4238</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8058</v>
+        <v>-2.3144</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1066</v>
+        <v>-1.1095</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6683</v>
+        <v>-2.0943</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.142</v>
+        <v>-1.9453</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5263</v>
+        <v>-0.149</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2116</v>
+        <v>-0.2419</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2254</v>
+        <v>-0.3633</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0138</v>
+        <v>0.1214</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4567</v>
+        <v>-1.8524</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9166</v>
+        <v>-1.582</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5401</v>
+        <v>-0.2704</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1721</v>
+        <v>-3.1255</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3576</v>
+        <v>0.0379</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4222</v>
+        <v>-0.1656</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0646</v>
+        <v>0.2035</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.027</v>
+        <v>-3.9124</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.6815</v>
+        <v>-2.8058</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6544</v>
+        <v>-1.1066</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.1037</v>
+        <v>-3.6683</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.0686</v>
+        <v>-3.142</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0351</v>
+        <v>-0.5263</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.7209</v>
+        <v>-1.2116</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5516</v>
+        <v>-1.2254</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.1694</v>
+        <v>0.0138</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3828</v>
+        <v>-2.4567</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.517</v>
+        <v>-1.9166</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1342</v>
+        <v>-0.5401</v>
       </c>
       <c r="P24" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1224</v>
+        <v>-0.3576</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4015</v>
+        <v>-0.4222</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2791</v>
+        <v>0.0646</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3869</v>
+        <v>-0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-5.027</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.6815</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.6544</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-5.1037</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.0686</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.0351</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.7209</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.5516</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.1694</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.3828</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.517</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1342</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.1224</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.4015</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484223_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-13.3645</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>-8.948399999999999</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>-4.416200000000001</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>-17.9505</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>-9.1852</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>-8.7652</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>-2.1713</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>1.1931</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>-3.3645</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>-15.7792</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N26" t="n">
         <v>-10.3785</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>-5.400799999999999</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>3.907</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-10.7438</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>14.6507</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>-1.9807</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>-2.5711</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>0.5906</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>2.6597</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>6.5378</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-3.8782</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
